--- a/themes/insurance.xlsx
+++ b/themes/insurance.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,304 +450,204 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Список компаний доступен по [ссылке](https://uralsib.ru/ipoteka/strakhovanie)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Список компаний доступен по [ссылке](https://uralsib.ru/ipoteka/strakhovanie).</t>
+          <t xml:space="preserve">          Подключить услугу страхования жизни и здоровья держателей кредитных карт «Моя защита» можно в «Уралсиб Онлайн» и в [офисе банка](OfficeLink), при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>похоже на опечатку/баг в коде (не в тексте): ссылка «[офисе банка](OfficeLink)» указывает на буквальный текст «OfficeLink» вместо переменной вида {{$temp.officeLink}}, как в остальной базе. Не исправлял сам, так как это код, но решил отметить</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Подключить услугу страхования жизни и здоровья держателей кредитных карт «Моя защита» можно в «Уралсиб Онлайн» и в [офисе банка](OfficeLink), при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">          1. На главном экране выберете нужную карту - вкладка «Сервисы».</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Сервисы».</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>похоже на опечатку/баг в коде (не в тексте): ссылка «[офисе банка](OfficeLink)» указывает на буквальный текст «OfficeLink» вместо переменной вида {{$temp.officeLink}}, как в остальной базе. Не исправлял сам, так как это код, но решил отметить</t>
+          <t>«выберете» (буд. время) исправлено на «выберите» (повелительное наклонение, как в аналогичных шагах); дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1. На главном экране выберете нужную карту - вкладка «Сервисы».</t>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту - вкладка «Управление».</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Сервисы».</t>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Управление».</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>«выберете» (буд. время) исправлено на «выберите» (повелительное наклонение, как в аналогичных шагах); дефис заменён на тире</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту - вкладка «Управление».</t>
+          <t xml:space="preserve">          2. Далее «Сервисы» - «Моя защита» - «Подключить».</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Управление».</t>
+          <t xml:space="preserve">          2. Далее «Сервисы» — «Моя защита» — «Подключить».</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>дефис заменён на тире</t>
+          <t>дефисы заменены на тире</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">          2. Далее «Сервисы» - «Моя защита» - «Подключить».</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Далее «Сервисы» — «Моя защита» — «Подключить».</t>
+          <t xml:space="preserve">          3. В [офисе банка](OfficeLink), при себе нужно иметь паспорт.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>дефисы заменены на тире</t>
+          <t>похоже на опечатку/баг в коде (не в тексте): ссылка «[офисе банка](OfficeLink)» указывает на буквальный текст «OfficeLink» вместо переменной. Не исправлял сам, но решил отметить</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Более подробно ознакомиться с условиями можно по [ссылке](https://uralsib.ru/strakhovanie/kreditnaya-karta)</t>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту - вкладка «Сервисы».</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Более подробно ознакомиться с условиями можно по [ссылке](https://uralsib.ru/strakhovanie/kreditnaya-karta).</t>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Сервисы».</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Ознакомиться с условиями страхования и подобрать подходящий продукт можно на [сайте](https://uralsib.ru/strakhovanie)</t>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту - вкладка «Управление».</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Ознакомиться с условиями страхования и подобрать подходящий продукт можно на [сайте](https://uralsib.ru/strakhovanie).</t>
+          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Управление».</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Продлить договор можно в любой страховой компании из [списка](https://uralsib.ru/ipoteka/strakhovanie)</t>
+          <t xml:space="preserve">          2. Далее «Сервисы» - «Моя защита» - «Отключить»</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Продлить договор можно в любой страховой компании из [списка](https://uralsib.ru/ipoteka/strakhovanie).</t>
+          <t xml:space="preserve">          2. Далее «Сервисы» — «Моя защита» — «Отключить»</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефисы заменены на тире</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Продлить КАСКО можно в любой страховой компании из [списка](https://www.uralsib.ru/legal/strakhovie-kompanii)</t>
+          <t xml:space="preserve">          Страхование залога от рисков повреждения и уничтожения - это обязательный вид страхования, который заключается на весь срок кредитования. </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">          Продлить КАСКО можно в любой страховой компании из [списка](https://www.uralsib.ru/legal/strakhovie-kompanii).</t>
+          <t xml:space="preserve">          Страхование залога от рисков повреждения и уничтожения — это обязательный вид страхования, который заключается на весь срок кредитования. </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>дефис заменён на тире (конструкция «X — это Y»)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>157</v>
+        <v>222</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">          3. В [офисе банка](OfficeLink), при себе нужно иметь паспорт.</t>
+          <t xml:space="preserve">          Полис ОСАГО – это обязательное страхование гражданской ответственности владельцев автомобиля и отказаться от него нельзя.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Полис ОСАГО — это обязательное страхование гражданской ответственности владельцев автомобиля и отказаться от него нельзя.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>похоже на опечатку/баг в коде (не в тексте): ссылка «[офисе банка](OfficeLink)» указывает на буквальный текст «OfficeLink» вместо переменной. Не исправлял сам, но решил отметить</t>
+          <t>эн-дефис заменён на тире (конструкция «X — это Y»)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>161</v>
+        <v>244</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту - вкладка «Сервисы».</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Сервисы».</t>
+          <t xml:space="preserve">          Для возврата неиспользованной части страховой премии, после полного досрочного погашения, обратитесь в [офис банка](OfficeLink) с заявлением.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>166</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту - вкладка «Управление».</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. На главном экране выберите нужную карту — вкладка «Управление».</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>167</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Далее «Сервисы» - «Моя защита» - «Отключить»</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Далее «Сервисы» — «Моя защита» — «Отключить».</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>дефисы заменены на тире; добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>189</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Страхование залога от рисков повреждения и уничтожения - это обязательный вид страхования, который заключается на весь срок кредитования. </t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Страхование залога от рисков повреждения и уничтожения — это обязательный вид страхования, который заключается на весь срок кредитования. </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>дефис заменён на тире (конструкция «X — это Y»)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>222</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Полис ОСАГО – это обязательное страхование гражданской ответственности владельцев автомобиля и отказаться от него нельзя.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Полис ОСАГО — это обязательное страхование гражданской ответственности владельцев автомобиля и отказаться от него нельзя.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>эн-дефис заменён на тире (конструкция «X — это Y»)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>244</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Для возврата неиспользованной части страховой премии, после полного досрочного погашения, обратитесь в [офис банка](OfficeLink) с заявлением.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
         <is>
           <t>похоже на опечатку/баг в коде (не в тексте): ссылка «[офис банка](OfficeLink)» указывает на буквальный текст «OfficeLink» вместо переменной. Не исправлял сам, но решил отметить</t>
         </is>
